--- a/项目进度总览.xlsx
+++ b/项目进度总览.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="24690" windowHeight="11490"/>
   </bookViews>
   <sheets>
     <sheet name="项目进度总览" sheetId="1" r:id="rId1"/>
-    <sheet name="状态分组" sheetId="2" r:id="rId2"/>
-    <sheet name="填写说明" sheetId="3" r:id="rId3"/>
+    <sheet name="收尾排期" sheetId="2" r:id="rId2"/>
+    <sheet name="状态分组" sheetId="3" r:id="rId3"/>
+    <sheet name="填写说明" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,9 +30,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="97">
-  <si>
-    <t>头程项目 · 进度总览（截至 2026-06-16）</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="157">
+  <si>
+    <t>头程项目 · 进度总览（截至 2026-06-22 · 含收尾排期）</t>
   </si>
   <si>
     <t>序号</t>
@@ -46,9 +47,18 @@
     <t>待解决问题</t>
   </si>
   <si>
+    <t>开发开始时间</t>
+  </si>
+  <si>
     <t>开发完成时间</t>
   </si>
   <si>
+    <t>开发人员</t>
+  </si>
+  <si>
+    <t>功能上线时间</t>
+  </si>
+  <si>
     <t>最终验收时间</t>
   </si>
   <si>
@@ -56,6 +66,9 @@
   </si>
   <si>
     <t>项目状态</t>
+  </si>
+  <si>
+    <t>其他备注</t>
   </si>
   <si>
     <t>整柜下单</t>
@@ -65,262 +78,430 @@
 客服已可下单；产品侧刚测完，处于优化阶段</t>
   </si>
   <si>
-    <t>测试暴露的问题仍在优化中：抓取船期、仓位用起运港目的港匹配、是否放舱功能放在列表等</t>
-  </si>
-  <si>
-    <t>第一版已经上线，优化预计 2026-06 月底</t>
+    <t>抓取船期、起运港目的港匹配、放舱功能放列表等优化项</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>余学康、王锦平</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>王锦平</t>
+  </si>
+  <si>
+    <t>验收中</t>
+  </si>
+  <si>
+    <t>P0 优化 6/24 前关闭，6/25–6/30 业务验收</t>
+  </si>
+  <si>
+    <t>散货询价</t>
+  </si>
+  <si>
+    <t>已在使用中</t>
+  </si>
+  <si>
+    <t>报表相关问题（不阻塞签收，后续迭代）</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>已上线</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>已验收</t>
+  </si>
+  <si>
+    <t>袁华君</t>
+  </si>
+  <si>
+    <t>已在使用</t>
+  </si>
+  <si>
+    <t>6 月已正式签收</t>
+  </si>
+  <si>
+    <t>整柜询价</t>
+  </si>
+  <si>
+    <t>刚上线；与袁经理沟通是否先在苏州试点</t>
+  </si>
+  <si>
+    <t>推广范围、苏州试点条件待袁经理确认</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>余学康</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>含推广决策；功能验收与试点方案同步确认</t>
+  </si>
+  <si>
+    <t>提成管理</t>
+  </si>
+  <si>
+    <t>与财务联调测试中</t>
+  </si>
+  <si>
+    <t>财务侧反馈问题修复、试算核对</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>开发组</t>
+  </si>
+  <si>
+    <t>杜小双</t>
+  </si>
+  <si>
+    <t>6/25 前修完 P0；6/26–6/30 财务试算验收</t>
+  </si>
+  <si>
+    <t>小小科技</t>
+  </si>
+  <si>
+    <t>在使用中；反馈已解决部分问题</t>
+  </si>
+  <si>
+    <t>剩余问题范围已确认，非阻塞项后续迭代</t>
+  </si>
+  <si>
+    <t>张炜</t>
+  </si>
+  <si>
+    <t>待办中心（询价/报关）</t>
+  </si>
+  <si>
+    <t>已打通：询价报价、报关资料两类待办</t>
+  </si>
+  <si>
+    <t>原有待办需清理；其他流程下阶段</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>本轮回响仅验收已上线两类待办</t>
+  </si>
+  <si>
+    <t>智能仓对接</t>
+  </si>
+  <si>
+    <t>开发完成，待业务签收</t>
+  </si>
+  <si>
+    <t>智能仓团队确认上线时间与联调结果</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>智能仓团队</t>
+  </si>
+  <si>
+    <t>6/23–6/27 联调确认并签收</t>
+  </si>
+  <si>
+    <t>TEMU 对接</t>
+  </si>
+  <si>
+    <t>开发完成，待平台推送上线</t>
+  </si>
+  <si>
+    <t>等待 TEMU 侧推送时间、联调确认</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>TEMU 团队</t>
+  </si>
+  <si>
+    <t>6/23–6/27 跟进平台侧并联调签收</t>
+  </si>
+  <si>
+    <t>服务商模版匹配</t>
+  </si>
+  <si>
+    <t>方案已定，开发/配置进行中</t>
+  </si>
+  <si>
+    <t>方案落地与联调细节</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>姚总</t>
+  </si>
+  <si>
+    <t>已排期（7月）</t>
+  </si>
+  <si>
+    <t>7/26–7/30 业务验收</t>
+  </si>
+  <si>
+    <t>现金流量表</t>
+  </si>
+  <si>
+    <t>开发中</t>
+  </si>
+  <si>
+    <t>需求细节、与财务联调</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>已排期（6月底）</t>
+  </si>
+  <si>
+    <t>7/1–7/15 财务试跑验收</t>
+  </si>
+  <si>
+    <t>报关行对接</t>
+  </si>
+  <si>
+    <t>开发中（原型/方案已有）</t>
+  </si>
+  <si>
+    <t>对接联调、上线前验收</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>吴慧俊</t>
+  </si>
+  <si>
+    <t>7/1–7/6 走 3–5 票真实单验收</t>
+  </si>
+  <si>
+    <t>进口商管理</t>
+  </si>
+  <si>
+    <t>功能完整性、与业务联调</t>
+  </si>
+  <si>
+    <t>7/1–7/15 业务联调验收</t>
+  </si>
+  <si>
+    <t>待办中心（其他流程）</t>
+  </si>
+  <si>
+    <t>未开始</t>
+  </si>
+  <si>
+    <t>其他流程待办完善，本周期不纳入收尾</t>
+  </si>
+  <si>
+    <t>未排期</t>
+  </si>
+  <si>
+    <t>下阶段</t>
+  </si>
+  <si>
+    <t>本轮回响范围外，单独立项</t>
+  </si>
+  <si>
+    <t>财务自动核销</t>
+  </si>
+  <si>
+    <t>需求尚未对齐</t>
+  </si>
+  <si>
+    <t>建议 8 月需求对齐后再排期</t>
+  </si>
+  <si>
+    <t>工单系统</t>
+  </si>
+  <si>
+    <t>未开始，未排期</t>
+  </si>
+  <si>
+    <t>需求、优先级、资源均未定</t>
+  </si>
+  <si>
+    <t>本轮回响范围外</t>
+  </si>
+  <si>
+    <t>APP 业务重构</t>
+  </si>
+  <si>
+    <t>范围、排期均未定</t>
   </si>
   <si>
     <t>待确认</t>
   </si>
   <si>
-    <t>测试/优化中</t>
-  </si>
-  <si>
-    <t>散货询价</t>
-  </si>
-  <si>
-    <t>已在使用中</t>
-  </si>
-  <si>
-    <t>报表相关的问题</t>
-  </si>
-  <si>
-    <t>已上线（使用中）</t>
-  </si>
-  <si>
-    <t>已验收</t>
-  </si>
-  <si>
-    <t>袁华君</t>
-  </si>
-  <si>
-    <t>已在使用</t>
-  </si>
-  <si>
-    <t>整柜询价</t>
-  </si>
-  <si>
-    <t>刚上线；与袁经理沟通是否先在苏州试点</t>
-  </si>
-  <si>
-    <t>推广范围、试点条件待袁经理确认</t>
-  </si>
-  <si>
-    <t>已上线</t>
-  </si>
-  <si>
-    <t>待确认（苏州试点未定）</t>
-  </si>
-  <si>
-    <t>提成管理</t>
-  </si>
-  <si>
-    <t>与财务联调测试中</t>
-  </si>
-  <si>
-    <t>测试阶段问题待财务侧反馈并修复</t>
-  </si>
-  <si>
-    <t>6月25</t>
-  </si>
-  <si>
-    <t>杜小双</t>
-  </si>
-  <si>
-    <t>小小科技</t>
-  </si>
-  <si>
-    <t>在使用中；反馈已解决部分问题</t>
-  </si>
-  <si>
-    <t>剩余问题范围、是否全部闭环待确认</t>
-  </si>
-  <si>
-    <t>张炜</t>
-  </si>
-  <si>
-    <t>待办中心</t>
-  </si>
-  <si>
-    <t>已打通：询价报价、报关资料两类待办</t>
-  </si>
-  <si>
-    <t>原有待办需清理；其他流程待逐步完善</t>
-  </si>
-  <si>
-    <t>部分完成（持续迭代）</t>
-  </si>
-  <si>
-    <t>部分完成在使用</t>
-  </si>
-  <si>
-    <t>服务商模版匹配</t>
-  </si>
-  <si>
-    <t>方案已定，开发/配置进行中</t>
-  </si>
-  <si>
-    <t>方案落地与联调细节</t>
-  </si>
-  <si>
-    <t>预计 2026-07 完成</t>
-  </si>
-  <si>
-    <t>待确认（建议 7 月内）</t>
-  </si>
-  <si>
-    <t>姚总</t>
-  </si>
-  <si>
-    <t>已排期（7月）</t>
-  </si>
-  <si>
-    <t>现金流量表</t>
-  </si>
-  <si>
-    <t>开发中</t>
-  </si>
-  <si>
-    <t>已排期待开发</t>
-  </si>
-  <si>
-    <t>预计 2026-06 月底</t>
-  </si>
-  <si>
-    <t>已排期（6月底）</t>
-  </si>
-  <si>
-    <t>财务自动核销</t>
-  </si>
-  <si>
-    <t>未开始</t>
-  </si>
-  <si>
-    <t>需求尚未对齐</t>
-  </si>
-  <si>
-    <t>未排期</t>
-  </si>
-  <si>
-    <t>报关行对接</t>
-  </si>
-  <si>
-    <t>开发中（原型/方案已有）</t>
-  </si>
-  <si>
-    <t>对接联调、上线前验收</t>
-  </si>
-  <si>
-    <t>预计 2026-06 月底上线</t>
-  </si>
-  <si>
-    <t>待确认（建议与上线同步）</t>
-  </si>
-  <si>
-    <t>吴慧俊</t>
-  </si>
-  <si>
-    <t>进口商管理</t>
-  </si>
-  <si>
-    <t>功能完整性、与业务联调</t>
-  </si>
-  <si>
-    <t>工单系统</t>
-  </si>
-  <si>
-    <t>未开始，未排期</t>
-  </si>
-  <si>
-    <t>需求、优先级、资源均未定</t>
-  </si>
-  <si>
-    <t>王锦平</t>
-  </si>
-  <si>
-    <t>APP 业务重构</t>
-  </si>
-  <si>
-    <t>范围、排期均未定</t>
+    <t>头程项目 · 收尾排期计划（2026-06-22 制定）</t>
+  </si>
+  <si>
+    <t>收尾批次</t>
+  </si>
+  <si>
+    <t>待收尾内容</t>
+  </si>
+  <si>
+    <t>开发完成（可验收）</t>
+  </si>
+  <si>
+    <t>最终验收</t>
+  </si>
+  <si>
+    <t>优先级</t>
+  </si>
+  <si>
+    <t>① 6/30 前签收（6项）</t>
+  </si>
+  <si>
+    <t>P0 优化项关闭 + 业务走单验收</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>功能验收 + 苏州试点方案确认</t>
+  </si>
+  <si>
+    <t>财务反馈修复 + 试算核对签收</t>
+  </si>
+  <si>
+    <t>已上线两类待办清理 + 签收</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>联调结果确认 + 正式签收</t>
+  </si>
+  <si>
+    <t>平台推送上线 + 联调签收</t>
+  </si>
+  <si>
+    <t>② 7 月开发+验收（4项）</t>
+  </si>
+  <si>
+    <t>6/30 上线 + 真实单验收</t>
+  </si>
+  <si>
+    <t>6/30 提测 + 财务试跑</t>
+  </si>
+  <si>
+    <t>6/30 上线 + 业务联调</t>
+  </si>
+  <si>
+    <t>7 月开发配置 + 联调</t>
+  </si>
+  <si>
+    <t>③ 已签收（2项）</t>
+  </si>
+  <si>
+    <t>④ 下阶段（4项）</t>
+  </si>
+  <si>
+    <t>需求与范围未定</t>
+  </si>
+  <si>
+    <t>需求对齐</t>
+  </si>
+  <si>
+    <t>需求/资源未定</t>
+  </si>
+  <si>
+    <t>范围未定</t>
+  </si>
+  <si>
+    <t>汇总</t>
+  </si>
+  <si>
+    <t>本轮回响需收尾</t>
+  </si>
+  <si>
+    <t>6 月验收 6 项 + 7 月开发验收 4 项 = 共 10 项</t>
+  </si>
+  <si>
+    <t>目标：7/30 前全部签收</t>
   </si>
   <si>
     <t>模块</t>
   </si>
   <si>
+    <t>开发完成</t>
+  </si>
+  <si>
+    <t>未开始/下阶段</t>
+  </si>
+  <si>
+    <t>字段</t>
+  </si>
+  <si>
     <t>说明</t>
   </si>
   <si>
-    <t>正式使用中</t>
-  </si>
-  <si>
-    <t>使用中，部分问题已解决</t>
-  </si>
-  <si>
-    <t>询价报价、报关资料待办已拉通</t>
-  </si>
-  <si>
-    <t>整柜</t>
-  </si>
-  <si>
-    <t>刚上线；客服已可下单</t>
-  </si>
-  <si>
-    <t>整柜询价/下单</t>
-  </si>
-  <si>
-    <t>产品测试完成，问题优化中</t>
-  </si>
-  <si>
-    <t>与财务联调测试</t>
-  </si>
-  <si>
-    <t>整柜推广</t>
-  </si>
-  <si>
-    <t>苏州试点方案与袁经理沟通中</t>
-  </si>
-  <si>
-    <t>开发中（6月底）</t>
-  </si>
-  <si>
-    <t>预计 2026-06 月底完成</t>
-  </si>
-  <si>
-    <t>开发中（7月）</t>
-  </si>
-  <si>
-    <t>待对需求</t>
-  </si>
-  <si>
-    <t>字段</t>
-  </si>
-  <si>
-    <t>当前业务/测试/上线状态</t>
-  </si>
-  <si>
-    <t>阻塞项、优化项、待确认事项</t>
-  </si>
-  <si>
-    <t>开发侧计划完成或实际上线时间</t>
-  </si>
-  <si>
-    <t>业务/财务正式签收时间（待补充）</t>
-  </si>
-  <si>
-    <t>负责验收的角色或姓名（待补充）</t>
-  </si>
-  <si>
-    <t>汇总状态，便于筛选：已在使用 / 测试优化中 / 开发中 / 未开始</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>原文未提供验收人与最终验收时间，表中标注「待确认」处请项目负责人补充</t>
+    <t>开发侧：功能开发/优化完毕，可进入业务验收</t>
+  </si>
+  <si>
+    <t>实际上线或提测可用时间</t>
+  </si>
+  <si>
+    <t>业务/财务正式签收时间（= 开发完成 + 业务验收窗口）</t>
+  </si>
+  <si>
+    <t>负责验收签字的角色或姓名</t>
+  </si>
+  <si>
+    <t>已在使用 / 验收中 / 已排期 / 未开始</t>
+  </si>
+  <si>
+    <t>收尾口径</t>
+  </si>
+  <si>
+    <t>本轮回响共 10 项需收尾：6 月验收 6 项 + 7 月开发验收 4 项</t>
+  </si>
+  <si>
+    <t>已签收 2 项（散货询价、小小科技）；下阶段 4 项暂不纳入</t>
+  </si>
+  <si>
+    <t>开发定「可验收日」，业务定「签收日」；验收窗口一般 3–10 个工作日</t>
   </si>
 </sst>
 </file>
@@ -351,14 +532,14 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="13"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
+      <b/>
+      <sz val="14"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -554,7 +735,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
+        <fgColor rgb="FFD9E1F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1014,7 +1195,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1034,29 +1215,32 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1404,22 +1588,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="32" customWidth="1"/>
-    <col min="5" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="9" width="14" customWidth="1"/>
+    <col min="10" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:8">
-      <c r="A1" s="8" t="s">
+    <row r="1" ht="28" customHeight="1" spans="1:12">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" ht="27" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1444,348 +1630,630 @@
       <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" ht="40.5" spans="1:8">
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="40.5" spans="1:12">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>18</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="27" spans="1:12">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>18</v>
+        <v>26</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" ht="27" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" ht="27" spans="1:12">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="L5" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" ht="27" spans="1:12">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>47</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" ht="27" spans="1:12">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" ht="27" spans="1:8">
+    </row>
+    <row r="8" ht="27" spans="1:12">
       <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>47</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" ht="27" spans="1:12">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="13" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="H9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" ht="27" spans="1:12">
       <c r="A10" s="2">
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>47</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" ht="27" spans="1:12">
       <c r="A11" s="2">
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" ht="27" spans="1:8">
+        <v>47</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" ht="27" spans="1:12">
       <c r="A12" s="2">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>47</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" ht="27" spans="1:12">
       <c r="A13" s="2">
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>47</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" ht="27" spans="1:12">
       <c r="A14" s="2">
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>47</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" ht="27" spans="1:12">
       <c r="A15" s="2">
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>54</v>
+        <v>27</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" ht="27" spans="1:12">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1795,180 +2263,541 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="26" customHeight="1" spans="1:7">
+      <c r="A1" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" ht="27" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" ht="27" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="G8" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" ht="27" spans="1:7">
+      <c r="A10" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" ht="27" spans="1:7">
+      <c r="A18" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>56</v>
-      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" ht="27" spans="1:7">
+      <c r="A23" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1977,83 +2806,397 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="5" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="2" max="2" width="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>146</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>90</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>91</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>92</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" ht="27" spans="1:2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>96</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
